--- a/data/trans_dic/P02E$contratada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 9,05</t>
+          <t>1,89; 8,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,39</t>
+          <t>0,52; 4,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,79</t>
+          <t>0,32; 3,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,44</t>
+          <t>0,67; 3,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,48</t>
+          <t>1,31; 4,61</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,77</t>
+          <t>0,54; 6,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,15</t>
+          <t>0,32; 3,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,02</t>
+          <t>0,8; 5,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,56</t>
+          <t>0,24; 2,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,72</t>
+          <t>0,6; 3,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,49</t>
+          <t>1,24; 4,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,08</t>
+          <t>0,51; 2,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,79</t>
+          <t>0,58; 2,88</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,56</t>
+          <t>0,64; 5,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 4,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,37</t>
+          <t>0,5; 4,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,82</t>
+          <t>0,6; 4,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,3</t>
+          <t>1,02; 5,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,92</t>
+          <t>0,3; 2,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,89</t>
+          <t>0,87; 3,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,94</t>
+          <t>0,93; 4,11</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,86</t>
+          <t>0,97; 5,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,28</t>
+          <t>0,74; 5,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,88</t>
+          <t>1,32; 6,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,26</t>
+          <t>0,37; 4,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,44</t>
+          <t>1,47; 5,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,5</t>
+          <t>1,31; 5,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,75</t>
+          <t>1,02; 3,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,37</t>
+          <t>1,66; 4,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,78</t>
+          <t>1,66; 4,66</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,23</t>
+          <t>0,85; 3,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,8</t>
+          <t>0,97; 2,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,69</t>
+          <t>1,39; 3,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,81</t>
+          <t>1,04; 2,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,78</t>
+          <t>1,26; 2,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,03</t>
+          <t>1,3; 3,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,57</t>
+          <t>1,16; 2,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,47</t>
+          <t>1,31; 2,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,94</t>
+          <t>1,61; 2,98</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 7376</t>
+          <t>0; 6236</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7866</t>
+          <t>0; 6831</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3068; 14513</t>
+          <t>3036; 13690</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 8103</t>
+          <t>0; 7202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2056; 13112</t>
+          <t>1547; 13015</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6360</t>
+          <t>0; 6547</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1027; 9798</t>
+          <t>1118; 10912</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3669; 17105</t>
+          <t>3310; 15296</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4028; 16011</t>
+          <t>4664; 16458</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1058; 13325</t>
+          <t>1065; 12389</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>969; 9581</t>
+          <t>962; 9465</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8840</t>
+          <t>0; 8707</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2913; 15367</t>
+          <t>2435; 15345</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1102; 11703</t>
+          <t>1111; 13243</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2069; 13312</t>
+          <t>2133; 12304</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5641; 22582</t>
+          <t>6237; 21666</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2960; 15811</t>
+          <t>3897; 16925</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3639; 16647</t>
+          <t>3435; 17181</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2008</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>975; 12275</t>
+          <t>1422; 12653</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7438</t>
+          <t>0; 6874</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>977; 8643</t>
+          <t>979; 8870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2113; 13531</t>
+          <t>2120; 15322</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2336; 13466</t>
+          <t>2593; 13855</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>971; 9485</t>
+          <t>975; 8886</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5413; 22374</t>
+          <t>5008; 19929</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4222; 16478</t>
+          <t>3905; 17158</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1656; 9985</t>
+          <t>1647; 9967</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1933; 13828</t>
+          <t>1938; 13692</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2516; 11424</t>
+          <t>2557; 13088</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1051; 12007</t>
+          <t>1045; 12251</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7028; 22073</t>
+          <t>5965; 21743</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4044; 16632</t>
+          <t>3962; 16310</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4359; 16990</t>
+          <t>4620; 16550</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11555; 29193</t>
+          <t>11051; 28820</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8159; 23739</t>
+          <t>8232; 23161</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5288; 20210</t>
+          <t>5347; 19648</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9777; 27556</t>
+          <t>9537; 27679</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10375; 27925</t>
+          <t>10492; 28417</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9755; 28288</t>
+          <t>10421; 28616</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18523; 42096</t>
+          <t>19166; 41051</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14305; 33665</t>
+          <t>14456; 34645</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17969; 41980</t>
+          <t>18906; 41571</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33115; 61772</t>
+          <t>32835; 61688</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29124; 54874</t>
+          <t>30033; 55725</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$contratada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,54</t>
+          <t>1,92; 8,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,36</t>
+          <t>0,66; 4,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,11</t>
+          <t>0,32; 3,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,08</t>
+          <t>0,69; 3,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,61</t>
+          <t>1,11; 4,62</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,29</t>
+          <t>0,54; 6,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,12</t>
+          <t>0,32; 3,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,01</t>
+          <t>0,88; 5,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,89</t>
+          <t>0,24; 2,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,44</t>
+          <t>0,57; 3,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,31</t>
+          <t>1,12; 4,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,22</t>
+          <t>0,42; 2,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,88</t>
+          <t>0,58; 2,74</t>
         </is>
       </c>
     </row>
@@ -903,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,73</t>
+          <t>0,81; 6,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 4,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,49</t>
+          <t>0,49; 4,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,32</t>
+          <t>0,59; 3,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,46</t>
+          <t>1,06; 5,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,73</t>
+          <t>0,3; 2,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,46</t>
+          <t>0,85; 3,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,11</t>
+          <t>0,98; 4,1</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,85</t>
+          <t>1,01; 5,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,23</t>
+          <t>0,73; 5,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,73</t>
+          <t>1,38; 6,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,34</t>
+          <t>0,43; 4,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,36</t>
+          <t>1,68; 5,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,4</t>
+          <t>1,31; 5,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,66</t>
+          <t>0,99; 3,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,32</t>
+          <t>1,72; 4,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,66</t>
+          <t>1,68; 4,7</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,14</t>
+          <t>0,92; 3,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,81</t>
+          <t>0,99; 2,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,76</t>
+          <t>1,52; 3,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,85</t>
+          <t>0,99; 2,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,71</t>
+          <t>1,25; 2,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,12</t>
+          <t>1,25; 3,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,55</t>
+          <t>1,19; 2,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,47</t>
+          <t>1,29; 2,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,98</t>
+          <t>1,55; 2,92</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6236</t>
+          <t>0; 7121</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6831</t>
+          <t>0; 7721</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3036; 13690</t>
+          <t>3081; 13973</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7202</t>
+          <t>0; 9109</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1547; 13015</t>
+          <t>1959; 12994</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6547</t>
+          <t>0; 7119</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1118; 10912</t>
+          <t>1134; 11152</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3310; 15296</t>
+          <t>3416; 15385</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4664; 16458</t>
+          <t>3983; 16521</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1065; 12389</t>
+          <t>1064; 13682</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>962; 9465</t>
+          <t>960; 9404</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8707</t>
+          <t>0; 10438</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2435; 15345</t>
+          <t>2704; 15467</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1111; 13243</t>
+          <t>1101; 11526</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2133; 12304</t>
+          <t>2050; 12051</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6237; 21666</t>
+          <t>5655; 22437</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3897; 16925</t>
+          <t>3217; 16705</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3435; 17181</t>
+          <t>3444; 16348</t>
         </is>
       </c>
     </row>
@@ -1748,42 +1748,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1422; 12653</t>
+          <t>1778; 13715</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6874</t>
+          <t>0; 7458</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>979; 8870</t>
+          <t>977; 8792</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2120; 15322</t>
+          <t>2091; 13938</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2593; 13855</t>
+          <t>2693; 14094</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>975; 8886</t>
+          <t>970; 8654</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5008; 19929</t>
+          <t>4890; 20528</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3905; 17158</t>
+          <t>4102; 17141</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1647; 9967</t>
+          <t>1717; 9649</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1938; 13692</t>
+          <t>1918; 14404</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2557; 13088</t>
+          <t>2687; 12415</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1045; 12251</t>
+          <t>1221; 12197</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5965; 21743</t>
+          <t>6827; 22938</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3962; 16310</t>
+          <t>3973; 16382</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4620; 16550</t>
+          <t>4501; 17763</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11051; 28820</t>
+          <t>11457; 29970</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8232; 23161</t>
+          <t>8355; 23333</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5347; 19648</t>
+          <t>5776; 21178</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9537; 27679</t>
+          <t>9748; 28174</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10492; 28417</t>
+          <t>11538; 27798</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10421; 28616</t>
+          <t>9967; 28037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19166; 41051</t>
+          <t>19027; 41013</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14456; 34645</t>
+          <t>13903; 33511</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18906; 41571</t>
+          <t>19499; 43188</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32835; 61688</t>
+          <t>32198; 61828</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30033; 55725</t>
+          <t>28981; 54461</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$contratada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$contratada-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa contratada (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
